--- a/albums/pink_floyd all.xlsx
+++ b/albums/pink_floyd all.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Лист1" sheetId="1" r:id="Rb2f857972bd74d8a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sources" sheetId="2" r:id="R0c6858400db64528"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Лист1" sheetId="1" r:id="R3d87350b3bc447b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sources" sheetId="2" r:id="R512dad54d13a417f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -387,10 +387,10 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultColWidth="12.630000114440918" defaultRowHeight="15.75"/>
   <x:cols>
-    <x:col min="1" max="1" width="8" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="52" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="46" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15.75" hidden="0" customHeight="1">
@@ -415,10 +415,10 @@
         <x:v>Pink Floyd</x:v>
       </x:c>
       <x:c r="C2" s="19" t="str">
-        <x:v>The Piper at the Gates of Dawn</x:v>
+        <x:v>The Endless River</x:v>
       </x:c>
       <x:c r="D2" s="19" t="str">
-        <x:v>psychedelic rock, psychedelic pop, space rock, 1967</x:v>
+        <x:v>ambient, progressive rock, instrumental rock, 2014</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15.75" hidden="0" customHeight="1">
@@ -429,10 +429,10 @@
         <x:v>Pink Floyd</x:v>
       </x:c>
       <x:c r="C3" s="19" t="str">
-        <x:v>A Saucerful of Secrets</x:v>
+        <x:v>The Division Bell</x:v>
       </x:c>
       <x:c r="D3" s="19" t="str">
-        <x:v>psychedelic rock, space rock, experimental rock, 1968</x:v>
+        <x:v>progressive rock, art rock, 1994</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15.75" hidden="0" customHeight="1">
@@ -443,10 +443,10 @@
         <x:v>Pink Floyd</x:v>
       </x:c>
       <x:c r="C4" s="19" t="str">
-        <x:v>Soundtrack from the Film More</x:v>
+        <x:v>A Momentary Lapse of Reason</x:v>
       </x:c>
       <x:c r="D4" s="19" t="str">
-        <x:v>psychedelic rock, hard rock, soundtrack, 1969</x:v>
+        <x:v>progressive rock, art rock, 1987</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15.75" hidden="0" customHeight="1">
@@ -457,10 +457,10 @@
         <x:v>Pink Floyd</x:v>
       </x:c>
       <x:c r="C5" s="19" t="str">
-        <x:v>Ummagumma</x:v>
+        <x:v>The Final Cut</x:v>
       </x:c>
       <x:c r="D5" s="19" t="str">
-        <x:v>progressive rock, psychedelic rock, experimental rock, 1969</x:v>
+        <x:v>progressive rock, art rock, concept album, 1983</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15.75" hidden="0" customHeight="1">
@@ -471,10 +471,10 @@
         <x:v>Pink Floyd</x:v>
       </x:c>
       <x:c r="C6" s="19" t="str">
-        <x:v>Atom Heart Mother</x:v>
+        <x:v>The Wall</x:v>
       </x:c>
       <x:c r="D6" s="19" t="str">
-        <x:v>progressive rock, psychedelic rock, symphonic rock, 1970</x:v>
+        <x:v>progressive rock, art rock, rock opera, 1979</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15.75" hidden="0" customHeight="1">
@@ -485,10 +485,10 @@
         <x:v>Pink Floyd</x:v>
       </x:c>
       <x:c r="C7" s="19" t="str">
-        <x:v>Meddle</x:v>
+        <x:v>Animals</x:v>
       </x:c>
       <x:c r="D7" s="19" t="str">
-        <x:v>progressive rock, psychedelic rock, space rock, 1971</x:v>
+        <x:v>progressive rock, art rock, 1977</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15.75" hidden="0" customHeight="1">
@@ -499,10 +499,10 @@
         <x:v>Pink Floyd</x:v>
       </x:c>
       <x:c r="C8" s="19" t="str">
-        <x:v>Obscured by Clouds</x:v>
+        <x:v>Wish You Were Here</x:v>
       </x:c>
       <x:c r="D8" s="19" t="str">
-        <x:v>progressive rock, psychedelic rock, soundtrack, 1972</x:v>
+        <x:v>progressive rock, art rock, space rock, 1975</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15.75" hidden="0" customHeight="1">
@@ -527,10 +527,10 @@
         <x:v>Pink Floyd</x:v>
       </x:c>
       <x:c r="C10" s="19" t="str">
-        <x:v>Wish You Were Here</x:v>
+        <x:v>Obscured by Clouds</x:v>
       </x:c>
       <x:c r="D10" s="19" t="str">
-        <x:v>progressive rock, art rock, space rock, 1975</x:v>
+        <x:v>progressive rock, psychedelic rock, soundtrack, 1972</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="15.75" hidden="0" customHeight="1">
@@ -541,10 +541,10 @@
         <x:v>Pink Floyd</x:v>
       </x:c>
       <x:c r="C11" s="19" t="str">
-        <x:v>Animals</x:v>
+        <x:v>Meddle</x:v>
       </x:c>
       <x:c r="D11" s="19" t="str">
-        <x:v>progressive rock, art rock, 1977</x:v>
+        <x:v>progressive rock, psychedelic rock, space rock, 1971</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15.75" hidden="0" customHeight="1">
@@ -555,10 +555,10 @@
         <x:v>Pink Floyd</x:v>
       </x:c>
       <x:c r="C12" s="19" t="str">
-        <x:v>The Wall</x:v>
+        <x:v>Atom Heart Mother</x:v>
       </x:c>
       <x:c r="D12" s="19" t="str">
-        <x:v>progressive rock, art rock, rock opera, 1979</x:v>
+        <x:v>progressive rock, psychedelic rock, symphonic rock, 1970</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="15.75" hidden="0" customHeight="1">
@@ -569,10 +569,10 @@
         <x:v>Pink Floyd</x:v>
       </x:c>
       <x:c r="C13" s="19" t="str">
-        <x:v>The Final Cut</x:v>
+        <x:v>Ummagumma</x:v>
       </x:c>
       <x:c r="D13" s="19" t="str">
-        <x:v>progressive rock, art rock, concept album, 1983</x:v>
+        <x:v>progressive rock, psychedelic rock, experimental rock, 1969</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15.75" hidden="0" customHeight="1">
@@ -583,10 +583,10 @@
         <x:v>Pink Floyd</x:v>
       </x:c>
       <x:c r="C14" s="19" t="str">
-        <x:v>A Momentary Lapse of Reason</x:v>
+        <x:v>Soundtrack from the Film More</x:v>
       </x:c>
       <x:c r="D14" s="19" t="str">
-        <x:v>progressive rock, art rock, 1987</x:v>
+        <x:v>psychedelic rock, hard rock, soundtrack, 1969</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="15.75" hidden="0" customHeight="1">
@@ -597,10 +597,10 @@
         <x:v>Pink Floyd</x:v>
       </x:c>
       <x:c r="C15" s="19" t="str">
-        <x:v>The Division Bell</x:v>
+        <x:v>A Saucerful of Secrets</x:v>
       </x:c>
       <x:c r="D15" s="19" t="str">
-        <x:v>progressive rock, art rock, 1994</x:v>
+        <x:v>psychedelic rock, space rock, experimental rock, 1968</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="15.75" hidden="0" customHeight="1">
@@ -611,10 +611,10 @@
         <x:v>Pink Floyd</x:v>
       </x:c>
       <x:c r="C16" s="19" t="str">
-        <x:v>The Endless River</x:v>
+        <x:v>The Piper at the Gates of Dawn</x:v>
       </x:c>
       <x:c r="D16" s="19" t="str">
-        <x:v>ambient, progressive rock, instrumental rock, 2014</x:v>
+        <x:v>psychedelic rock, psychedelic pop, space rock, 1967</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -1130,7 +1130,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Redfa91efb52a479e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R69c212fe1e264d29"/>
   </x:tableParts>
 </x:worksheet>
 </file>
